--- a/output/pdf_financials_xlsx/FG.xlsx
+++ b/output/pdf_financials_xlsx/FG.xlsx
@@ -1279,13 +1279,13 @@
         <v>0.340567</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.055135</v>
+        <v>-1.055135</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>-0.48071</v>
@@ -1325,16 +1325,16 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.07654900000000001</v>
+        <v>-0.591155</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.06339599999999999</v>
+        <v>-0.976302</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.285884</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.681134</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1567,25 +1567,25 @@
         <v>-0.046567</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.257303</v>
+        <v>-0.257303</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.456453</v>
+        <v>-0.456453</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.642942</v>
+        <v>-0.642942</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.340567</v>
+        <v>-0.340567</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.055135</v>
+        <v>-1.055135</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-0.48071</v>
@@ -1741,25 +1741,25 @@
         <v>-0.046567</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.257303</v>
+        <v>-0.257303</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.456453</v>
+        <v>-0.456453</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.642942</v>
+        <v>-0.642942</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.340567</v>
+        <v>-0.340567</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.055135</v>
+        <v>-1.055135</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>-0.48071</v>
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-5.14606</v>
+        <v>5.14606</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-11.411325</v>
+        <v>11.411325</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-32.1471</v>
+        <v>32.1471</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-7.536679</v>
+        <v>7.536679</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-8.615069</v>
+        <v>8.615069</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-20.2602</v>
+        <v>20.2602</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>24.0355</v>
@@ -2003,13 +2003,13 @@
         <v>0.340567</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.055135</v>
+        <v>-1.055135</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.48071</v>
@@ -2119,13 +2119,13 @@
         <v>0.341299</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.055867</v>
+        <v>-1.054403</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.48071</v>
@@ -2257,25 +2257,25 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>22.92902244108167</v>
+        <v>177.0709775589183</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12.19507972507401</v>
+        <v>187.804920274926</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>-0</v>
@@ -6017,10 +6017,10 @@
         <v>2.128568</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.22849</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.30754</v>
       </c>
     </row>
     <row r="93">
@@ -9677,7 +9677,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10879,7 +10883,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -41197,19 +41205,19 @@
         </is>
       </c>
       <c r="J327" s="5" t="n">
-        <v>0.340567</v>
+        <v>-0.340567</v>
       </c>
       <c r="K327" s="5" t="n">
-        <v>1.055135</v>
+        <v>-1.055135</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>1.378411</v>
+        <v>-1.378411</v>
       </c>
       <c r="M327" s="5" t="n">
-        <v>0.607806</v>
+        <v>-0.607806</v>
       </c>
       <c r="N327" s="5" t="n">
-        <v>0.48071</v>
+        <v>-0.48071</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -45487,16 +45495,16 @@
         </is>
       </c>
       <c r="G370" s="5" t="n">
-        <v>0.257303</v>
+        <v>-0.257303</v>
       </c>
       <c r="H370" s="5" t="n">
-        <v>0.456453</v>
+        <v>-0.456453</v>
       </c>
       <c r="I370" s="5" t="n">
-        <v>0.642942</v>
+        <v>-0.642942</v>
       </c>
       <c r="J370" s="5" t="n">
-        <v>0.340567</v>
+        <v>-0.340567</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FG.xlsx
+++ b/output/pdf_financials_xlsx/FG.xlsx
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003827</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1985,7 +1985,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.038926</v>
+        <v>-0.042753</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.046567</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.038926</v>
+        <v>-0.042753</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.046567</v>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.507771</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.4261</v>
@@ -2426,19 +2426,19 @@
         <v>0.005042</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.013936</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.0008229999999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.005779</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.031928</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.052883</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>0.121333</v>
@@ -2453,10 +2453,10 @@
         <v>0.326356</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.055748</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.042723</v>
       </c>
     </row>
     <row r="35">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.507771</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.4261</v>
@@ -2542,19 +2542,19 @@
         <v>0.005042</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.013936</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.0008229999999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.005779</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.031928</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.052883</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>0.181333</v>
@@ -2569,10 +2569,10 @@
         <v>0.445317</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.217038</v>
+        <v>0.272786</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.175216</v>
+        <v>0.217939</v>
       </c>
     </row>
     <row r="37">
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.510271</v>
+        <v>0.0025</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.116483</v>
@@ -3238,19 +3238,19 @@
         <v>0.058515</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.056303</v>
+        <v>0.042367</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.026173</v>
+        <v>0.02535</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.031338</v>
+        <v>0.025559</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.097611</v>
+        <v>0.06568300000000001</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.078233</v>
+        <v>0.02535</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.0233</v>
@@ -3265,7 +3265,7 @@
         <v>0.193655</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.156561</v>
+        <v>0.100813</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -38285,7 +38285,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -47820,7 +47820,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" s="5" t="n">

--- a/output/pdf_financials_xlsx/FG.xlsx
+++ b/output/pdf_financials_xlsx/FG.xlsx
@@ -7132,7 +7132,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.001796</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -7588,7 +7588,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.75488</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -26203,7 +26203,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -28316,7 +28320,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/FG.xlsx
+++ b/output/pdf_financials_xlsx/FG.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.011418</v>
+        <v>0.027386</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.014092</v>
+        <v>0.031453</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.110283</v>
@@ -1325,7 +1325,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.591155</v>
+        <v>-0.138207</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.976302</v>
@@ -2257,7 +2257,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>177.0709775589183</v>
+        <v>41.39768520182596</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>187.804920274926</v>
@@ -6473,10 +6473,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002214</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005725</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -7321,10 +7321,10 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.076672</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.012008</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -18231,7 +18231,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -21427,7 +21431,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -28425,7 +28433,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -29350,7 +29362,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -30679,7 +30695,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E222" s="5" t="n">
         <v>0.002214</v>
       </c>
@@ -47119,7 +47139,11 @@
           <t>Future income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -48034,7 +48058,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E395" s="5" t="n">
         <v>0.015968</v>
       </c>
